--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104472_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104472_W2.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3761</v>
+        <v>3.1929</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3344</v>
+        <v>2.4256</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9583</v>
+        <v>0.7673</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4585</v>
+        <v>1.6865</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4318</v>
+        <v>0.034</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0267</v>
+        <v>1.6524</v>
       </c>
       <c r="J2" t="n">
-        <v>4.052</v>
+        <v>1.8409</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4176</v>
+        <v>0.5376</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6344</v>
+        <v>1.3033</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5935</v>
+        <v>-0.1544</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0142</v>
+        <v>-0.5036</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6077</v>
+        <v>0.3492</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2371</v>
+        <v>-0.1765</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0971</v>
+        <v>0.427</v>
       </c>
       <c r="U2" t="n">
-        <v>0.14</v>
+        <v>-0.6034</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6083</v>
+        <v>2.7108</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6049</v>
+        <v>4.0475</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0034</v>
+        <v>-1.3367</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8004</v>
+        <v>3.4368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3765</v>
+        <v>3.4022</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4239</v>
+        <v>0.0346</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3917</v>
+        <v>4.0072</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2051</v>
+        <v>3.3742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1866</v>
+        <v>0.633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4088</v>
+        <v>-0.5704</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1715</v>
+        <v>0.028</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2373</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6057</v>
+        <v>0.5911</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5989</v>
+        <v>0.8613</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0068</v>
+        <v>-0.2702</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4783</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5064</v>
+        <v>1.9372</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8959</v>
+        <v>3.808</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6105</v>
+        <v>-1.8707</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6679</v>
+        <v>2.4448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0258</v>
+        <v>0.1747</v>
       </c>
       <c r="I4" t="n">
-        <v>1.642</v>
+        <v>2.2701</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8531</v>
+        <v>3.6759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.547</v>
+        <v>0.9653</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3061</v>
+        <v>2.7106</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1852</v>
+        <v>-1.231</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5212</v>
+        <v>-0.7906</v>
       </c>
       <c r="O4" t="n">
-        <v>0.336</v>
+        <v>-0.4405</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.842</v>
+        <v>-0.3287</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1179</v>
+        <v>0.1321</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7241</v>
+        <v>-0.4607</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0045</v>
+        <v>1.58</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9955</v>
+        <v>1.1424</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.991</v>
+        <v>0.4376</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4368</v>
+        <v>1.8124</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1658</v>
+        <v>1.3785</v>
       </c>
       <c r="I5" t="n">
-        <v>2.271</v>
+        <v>0.4339</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6912</v>
+        <v>1.3788</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9697</v>
+        <v>1.1926</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7214</v>
+        <v>0.1862</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2543</v>
+        <v>0.4336</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8038999999999999</v>
+        <v>0.1859</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4504</v>
+        <v>0.2477</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.247</v>
+        <v>0.5612</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6956</v>
+        <v>0.1506</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5514</v>
+        <v>0.4105</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-1.4764</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2497</v>
+        <v>1.1949</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2945</v>
+        <v>0.1576</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5441</v>
+        <v>1.0373</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7978</v>
+        <v>2.787</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6249</v>
+        <v>1.6147</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1728</v>
+        <v>1.1723</v>
       </c>
       <c r="J6" t="n">
-        <v>1.744</v>
+        <v>1.7072</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9657</v>
+        <v>0.9405</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0538</v>
+        <v>1.0798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8676</v>
+        <v>-0.9092</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9043</v>
+        <v>-0.4114</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9633</v>
+        <v>-0.4978</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1824</v>
+        <v>0.9412</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7188</v>
+        <v>3.0323</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5364</v>
+        <v>-2.0911</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7228</v>
+        <v>2.7019</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1444</v>
+        <v>2.1318</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5784</v>
+        <v>0.5702</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0176</v>
+        <v>2.971</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8316</v>
+        <v>1.8024</v>
       </c>
       <c r="L7" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2948</v>
+        <v>-0.269</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0867</v>
+        <v>-0.3055</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5353</v>
+        <v>-0.1584</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5514</v>
+        <v>-0.1471</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0827</v>
+        <v>-0.4191</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1454</v>
+        <v>-1.3226</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0627</v>
+        <v>0.9035</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5963</v>
+        <v>-1.5859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4934</v>
+        <v>0.4994</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0897</v>
+        <v>-2.0853</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6615</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0244</v>
+        <v>-0.0312</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9348</v>
+        <v>-0.9139</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0042</v>
+        <v>-0.36</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2571</v>
+        <v>-0.4231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2528</v>
+        <v>0.0631</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1156</v>
+        <v>-1.0008</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5302</v>
+        <v>-2.4219</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4147</v>
+        <v>1.4211</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8676</v>
+        <v>-0.8703</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6277</v>
+        <v>-0.6289</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2399</v>
+        <v>-0.2414</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4808</v>
+        <v>-1.4876</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0696</v>
+        <v>0.1881</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3478</v>
+        <v>0.3485</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6048</v>
+        <v>-1.4086</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1024</v>
+        <v>-0.927</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5024</v>
+        <v>-0.4816</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5635</v>
+        <v>-0.5585</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0518</v>
+        <v>1.0594</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6153</v>
+        <v>-1.6178</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2628</v>
+        <v>-1.2775</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0217</v>
+        <v>1.017</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6992</v>
+        <v>0.719</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1754</v>
+        <v>0.0117</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1603</v>
+        <v>0.3505</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3357</v>
+        <v>-0.3388</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6558</v>
+        <v>-3.9382</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0603</v>
+        <v>-1.5301</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5955</v>
+        <v>-2.4081</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7454</v>
+        <v>-0.7731</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2831</v>
+        <v>1.262</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0285</v>
+        <v>-2.0351</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8714</v>
+        <v>-0.9198</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0799</v>
+        <v>1.0472</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9513</v>
+        <v>-1.967</v>
       </c>
       <c r="M11" t="n">
-        <v>0.126</v>
+        <v>0.1467</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2052</v>
+        <v>-0.461</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6956</v>
+        <v>-0.1048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0828</v>
+        <v>-4.7213</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8721</v>
+        <v>-4.4706</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2107</v>
+        <v>-0.2506</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1734</v>
+        <v>-2.1665</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1269</v>
+        <v>0.1318</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3003</v>
+        <v>-2.2984</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6118</v>
+        <v>-1.625</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5617</v>
+        <v>-0.5416</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.5759</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1688</v>
+        <v>-0.2342</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6142999999999983</v>
+        <v>0.06899999999999995</v>
       </c>
       <c r="E13" t="n">
-        <v>3.544600000000001</v>
+        <v>3.941199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.158899999999999</v>
+        <v>-3.871999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>8.937999999999999</v>
+        <v>8.915100000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>11.0967</v>
+        <v>11.0596</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1589</v>
+        <v>-2.1445</v>
       </c>
       <c r="J13" t="n">
-        <v>9.861299999999998</v>
+        <v>9.599200000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>10.1685</v>
+        <v>9.9903</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3072000000000006</v>
+        <v>-0.3911000000000004</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9232999999999998</v>
+        <v>-0.6839000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9286000000000001</v>
+        <v>1.0693</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8517</v>
+        <v>-1.7533</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.1052</v>
       </c>
       <c r="R13" t="n">
-        <v>9.073400000000001</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4497</v>
+        <v>-1.7647</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3928999999999997</v>
+        <v>0.3217000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0569</v>
+        <v>-2.0863</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.102399999999999</v>
+        <v>-7.0816</v>
       </c>
       <c r="W13" t="n">
-        <v>3.1497</v>
+        <v>3.1256</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.2521</v>
+        <v>-10.2071</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3781</v>
+        <v>5.0422</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0797</v>
+        <v>4.9242</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2984</v>
+        <v>0.118</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2343</v>
+        <v>-1.2271</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0202</v>
+        <v>-3.0132</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7859</v>
+        <v>1.7861</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3204</v>
+        <v>0.2918</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1296</v>
+        <v>-1.1451</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5547</v>
+        <v>-1.5189</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="O14" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4932</v>
+        <v>1.1602</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7743</v>
+        <v>0.6614</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7189</v>
+        <v>0.4988</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5274</v>
+        <v>2.1836</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2556</v>
+        <v>2.0397</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2718</v>
+        <v>0.1439</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9811</v>
+        <v>0.9673</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5006</v>
+        <v>1.4844</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6781</v>
+        <v>1.6404</v>
       </c>
       <c r="K15" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5192</v>
+        <v>1.496</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.6731</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1588</v>
+        <v>0.5122</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3811</v>
+        <v>0.448</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2223</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5481</v>
+        <v>0.6474</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5532</v>
+        <v>1.0152</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0051</v>
+        <v>-0.3679</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5281</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1917</v>
+        <v>-1.2001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6637</v>
+        <v>0.6613</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8803</v>
+        <v>0.8354</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1794</v>
+        <v>0.1509</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7009</v>
+        <v>0.6845</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4083</v>
+        <v>-1.3742</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3711</v>
+        <v>-1.351</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0003</v>
+        <v>0.1242</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2511</v>
+        <v>-0.2189</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2507</v>
+        <v>0.343</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5157</v>
+        <v>0.2676</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0869</v>
+        <v>0.587</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.3194</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5491</v>
+        <v>-0.5405</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9942</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5433</v>
+        <v>-1.537</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6701</v>
+        <v>0.6469</v>
       </c>
       <c r="K17" t="n">
-        <v>2.019</v>
+        <v>2.0027</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3488</v>
+        <v>-1.3559</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2193</v>
+        <v>-1.1874</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8115</v>
+        <v>0.5609</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8438</v>
+        <v>0.3758</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0324</v>
+        <v>0.1851</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0394</v>
+        <v>0.0014</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.7779</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5933</v>
+        <v>-0.7766</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0384</v>
+        <v>-0.2854</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7026</v>
+        <v>-0.5576</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.741</v>
+        <v>0.2723</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.2603</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6797</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9383</v>
+        <v>0.1708</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7798</v>
+        <v>-0.5457</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9771</v>
+        <v>-0.6471</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1973</v>
+        <v>0.1014</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3451</v>
+        <v>-0.1685</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1875</v>
+        <v>0.5177</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5326</v>
+        <v>-0.6862</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6552</v>
+        <v>-0.4884</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0353</v>
+        <v>0.4211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3801</v>
+        <v>-0.9095</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1241</v>
+        <v>-0.0344</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4919</v>
+        <v>0.7091</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3679</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3711</v>
+        <v>0.7257</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.483</v>
+        <v>1.672</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>-0.9463</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.753</v>
+        <v>-0.7601</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0089</v>
+        <v>-0.9629</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2559</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4008</v>
+        <v>-0.1173</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2411</v>
+        <v>-0.3046</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1597</v>
+        <v>0.1873</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.2472</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8253</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8147</v>
+        <v>-0.706</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0107</v>
+        <v>0.0704</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1484</v>
+        <v>-1.1418</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7543</v>
+        <v>-0.7537</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5576</v>
+        <v>-0.5685</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5908</v>
+        <v>-0.5733</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3575</v>
+        <v>-0.1767</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2571</v>
+        <v>-0.1375</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1004</v>
+        <v>-0.0392</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9831</v>
+        <v>-1.5939</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0335</v>
+        <v>-1.977</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9495</v>
+        <v>0.3832</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2859</v>
+        <v>-1.9727</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5658</v>
+        <v>-3.0961</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2798</v>
+        <v>1.1235</v>
       </c>
       <c r="J21" t="n">
-        <v>0.278</v>
+        <v>-0.7708</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0968</v>
+        <v>-1.9175</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1812</v>
+        <v>1.1467</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5639</v>
+        <v>-1.2018</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6626</v>
+        <v>-1.1786</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.0232</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1508</v>
+        <v>0.1998</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3115</v>
+        <v>-0.3349</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8393</v>
+        <v>0.5347</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4244</v>
+        <v>-2.36</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8447</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5796</v>
+        <v>-1.7415</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0311</v>
+        <v>-2.0173</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5139</v>
+        <v>-1.4973</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5171</v>
+        <v>-0.52</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9718</v>
+        <v>-0.985</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0593</v>
+        <v>-1.0323</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8834</v>
+        <v>-0.8628</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3006</v>
+        <v>-0.2532</v>
       </c>
       <c r="T22" t="n">
-        <v>0.127</v>
+        <v>0.3665</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4277</v>
+        <v>-0.6198</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4277</v>
+        <v>-2.4363</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6421</v>
+        <v>-2.5916</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2145</v>
+        <v>0.1553</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9797</v>
+        <v>-2.1246</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0966</v>
+        <v>-2.4956</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1169</v>
+        <v>0.3711</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-1.3921</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8986</v>
+        <v>-1.5038</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1541</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2352</v>
+        <v>-0.7325</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.198</v>
+        <v>-0.9918</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0372</v>
+        <v>0.2593</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6333</v>
+        <v>0.62</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0434</v>
+        <v>0.7126</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4101</v>
+        <v>-0.0926</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4141</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6142000000000003</v>
+        <v>0.6280000000000006</v>
       </c>
       <c r="E24" t="n">
-        <v>4.159</v>
+        <v>3.8721</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5445</v>
+        <v>-3.2441</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.937999999999999</v>
+        <v>-8.915299999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>-11.0968</v>
+        <v>-11.0595</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1591</v>
+        <v>2.1446</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9232999999999997</v>
+        <v>0.6841000000000006</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9282999999999996</v>
+        <v>-1.0693</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8518</v>
+        <v>1.7532</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.861400000000001</v>
+        <v>-9.599299999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-10.1685</v>
+        <v>-9.9903</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3072</v>
+        <v>0.3911</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>9.999999999993348e-05</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>9.073400000000001</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4499</v>
+        <v>2.4616</v>
       </c>
       <c r="T24" t="n">
-        <v>2.056699999999999</v>
+        <v>2.0861</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3930999999999999</v>
+        <v>0.3752999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1025</v>
+        <v>7.081699999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>10.2521</v>
+        <v>10.2072</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.1496</v>
+        <v>-3.1255</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104472_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104472_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.2071</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104472_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-3.1255</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
